--- a/examples/1UBQ/InterfaceScout_1UBQ_all_results.xlsx
+++ b/examples/1UBQ/InterfaceScout_1UBQ_all_results.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Patch_Members" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Run_Method'!$A$1:$B$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Run_Method'!$A$1:$B$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Map_Definitions'!$A$1:$F$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Residue_Values'!$A$1:$O$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Patches'!$A$1:$R$111</definedName>
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -709,107 +709,105 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>method.parameter_selection.selection_workflow_run</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>34329264963</v>
+          <t>method.parameter_selection.uses_experimental_adsorption_labels</t>
+        </is>
+      </c>
+      <c r="B26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>method.parameter_selection.selection_commit</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ba0e63b7b82a222856ff75a6dd39409b89b664dd</t>
-        </is>
+          <t>method.patch_radius_A</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>method.parameter_selection.uses_experimental_adsorption_labels</t>
-        </is>
-      </c>
-      <c r="B28" t="b">
-        <v>0</v>
+          <t>method.patch_definition</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>non-transitive local surface neighbourhood around a chemistry-patch maximum</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>method.patch_radius_A</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>8</v>
+          <t>method.orientation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>coarse outward C-alpha face consistency</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>method.patch_definition</t>
+          <t>method.ranking</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>non-transitive local surface neighbourhood around a chemistry-patch maximum</t>
+          <t>Pareto fronts across chemistry support, accessibility, patch coherence and orientation coherence; no weighted sum</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>method.orientation</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>coarse outward C-alpha face consistency</t>
-        </is>
+          <t>method.single_pass_all_maps</t>
+        </is>
+      </c>
+      <c r="B31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>method.ranking</t>
+          <t>scope.prediction_unit</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pareto fronts across chemistry support, accessibility, patch coherence and orientation coherence; no weighted sum</t>
+          <t>coarse protein surface region / interface patch</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>method.single_pass_all_maps</t>
+          <t>scope.predicts_absolute_adsorption_free_energy</t>
         </is>
       </c>
       <c r="B33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>scope.prediction_unit</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>coarse protein surface region / interface patch</t>
-        </is>
+          <t>scope.predicts_adsorption_amount</t>
+        </is>
+      </c>
+      <c r="B34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>scope.predicts_absolute_adsorption_free_energy</t>
+          <t>scope.predicts_unique_orientation</t>
         </is>
       </c>
       <c r="B35" t="b">
@@ -819,7 +817,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>scope.predicts_adsorption_amount</t>
+          <t>scope.models_adsorption_induced_unfolding</t>
         </is>
       </c>
       <c r="B36" t="b">
@@ -829,7 +827,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>scope.predicts_unique_orientation</t>
+          <t>scope.benchmark_fitted_weights</t>
         </is>
       </c>
       <c r="B37" t="b">
@@ -839,7 +837,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>scope.models_adsorption_induced_unfolding</t>
+          <t>scope.residue_precision_claim</t>
         </is>
       </c>
       <c r="B38" t="b">
@@ -849,61 +847,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>scope.benchmark_fitted_weights</t>
-        </is>
-      </c>
-      <c r="B39" t="b">
-        <v>0</v>
+          <t>diagnostics.n_surface_residues</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>scope.residue_precision_claim</t>
-        </is>
-      </c>
-      <c r="B40" t="b">
-        <v>0</v>
+          <t>diagnostics.surface_residue_keys</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A:1:; A:2:; A:4:; A:6:; A:7:; A:8:; A:9:; A:10:; A:11:; A:12:; A:14:; A:16:; A:18:; A:19:; A:20:; A:21:; A:22:; A:24:; A:25:; A:27:; A:28:; A:29:; A:31:; A:32:; A:33:; A:34:; A:35:; A:36:; A:37:; A:38:; A:39:; A:40:; A:42:; A:44:; A:45:; A:46:; A:47:; A:48:; A:49:; A:51:; A:52:; A:53:; A:54:; A:55:; A:57:; A:58:; A:59:; A:60:; A:62:; A:63:; A:64:; A:65:; A:66:; A:68:; A:70:; A:71:; A:72:; A:73:; A:74:; A:75:; A:76:</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>diagnostics.n_surface_residues</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>61</v>
+          <t>composite_policy.type</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>derived_overlay</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>diagnostics.surface_residue_keys</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>A:1:; A:2:; A:4:; A:6:; A:7:; A:8:; A:9:; A:10:; A:11:; A:12:; A:14:; A:16:; A:18:; A:19:; A:20:; A:21:; A:22:; A:24:; A:25:; A:27:; A:28:; A:29:; A:31:; A:32:; A:33:; A:34:; A:35:; A:36:; A:37:; A:38:; A:39:; A:40:; A:42:; A:44:; A:45:; A:46:; A:47:; A:48:; A:49:; A:51:; A:52:; A:53:; A:54:; A:55:; A:57:; A:58:; A:59:; A:60:; A:62:; A:63:; A:64:; A:65:; A:66:; A:68:; A:70:; A:71:; A:72:; A:73:; A:74:; A:75:; A:76:</t>
-        </is>
+          <t>composite_policy.validated_as_combined_model</t>
+        </is>
+      </c>
+      <c r="B42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>composite_policy.type</t>
+          <t>composite_policy.default_residue_rule</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>derived_overlay</t>
+          <t>maximum normalized support across selected canonical chemistry maps</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>composite_policy.validated_as_combined_model</t>
+          <t>composite_policy.double_counting</t>
         </is>
       </c>
       <c r="B44" t="b">
@@ -913,39 +913,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>composite_policy.default_residue_rule</t>
+          <t>composite_policy.weights</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>maximum normalized support across selected canonical chemistry maps</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>composite_policy.double_counting</t>
-        </is>
-      </c>
-      <c r="B46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>composite_policy.weights</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
           <t>none unless externally known surface composition is supplied in a future explicit model extension</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B47"/>
+  <autoFilter ref="A1:B45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1180,7 +1158,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oxide-like surface chemistry represented by the frozen carboxylate-compatible oxide channel.</t>
+          <t>Oxide-like surface chemistry represented by the carboxylate-compatible oxide channel.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3242,7 +3220,7 @@
         <v>0.7336400000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9155674811557055</v>
+        <v>0.9155674811557053</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -3382,7 +3360,7 @@
         <v>0.35205</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9282147875465802</v>
+        <v>0.9282147875465803</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -3452,7 +3430,7 @@
         <v>0.21375</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8804461556445288</v>
+        <v>0.8804461556445285</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -3802,7 +3780,7 @@
         <v>0.19109</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8844202509543376</v>
+        <v>0.8844202509543375</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -4852,7 +4830,7 @@
         <v>0.42832</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9155674811557055</v>
+        <v>0.9155674811557053</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -5272,7 +5250,7 @@
         <v>0.14937</v>
       </c>
       <c r="P32" t="n">
-        <v>0.8844202509543376</v>
+        <v>0.8844202509543375</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5482,7 +5460,7 @@
         <v>0.68184</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9026380252110359</v>
+        <v>0.9026380252110358</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5622,7 +5600,7 @@
         <v>0.42896</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8804461556445288</v>
+        <v>0.8804461556445285</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5692,7 +5670,7 @@
         <v>0.42498</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9756428370230283</v>
+        <v>0.9756428370230285</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5762,7 +5740,7 @@
         <v>0.50729</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9282147875465802</v>
+        <v>0.9282147875465803</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -7232,7 +7210,7 @@
         <v>0.73103</v>
       </c>
       <c r="P60" t="n">
-        <v>0.9155674811557055</v>
+        <v>0.9155674811557053</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -7372,7 +7350,7 @@
         <v>0.3555</v>
       </c>
       <c r="P62" t="n">
-        <v>0.9282147875465802</v>
+        <v>0.9282147875465803</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -7442,7 +7420,7 @@
         <v>0.21375</v>
       </c>
       <c r="P63" t="n">
-        <v>0.8804461556445288</v>
+        <v>0.8804461556445285</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -7792,7 +7770,7 @@
         <v>0.19109</v>
       </c>
       <c r="P68" t="n">
-        <v>0.8844202509543376</v>
+        <v>0.8844202509543375</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -8142,7 +8120,7 @@
         <v>0.40706</v>
       </c>
       <c r="P73" t="n">
-        <v>0.9415643206113605</v>
+        <v>0.9415643206113606</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -8422,7 +8400,7 @@
         <v>0.19638</v>
       </c>
       <c r="P77" t="n">
-        <v>0.9282147875465802</v>
+        <v>0.9282147875465803</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -8982,7 +8960,7 @@
         <v>0.31882</v>
       </c>
       <c r="P85" t="n">
-        <v>0.9282147875465802</v>
+        <v>0.9282147875465803</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -9052,7 +9030,7 @@
         <v>0.29293</v>
       </c>
       <c r="P86" t="n">
-        <v>0.9155674811557055</v>
+        <v>0.9155674811557053</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -9402,7 +9380,7 @@
         <v>0.40706</v>
       </c>
       <c r="P91" t="n">
-        <v>0.9415643206113605</v>
+        <v>0.9415643206113606</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9682,7 +9660,7 @@
         <v>0.19638</v>
       </c>
       <c r="P95" t="n">
-        <v>0.9282147875465802</v>
+        <v>0.9282147875465803</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -9822,7 +9800,7 @@
         <v>0.18459</v>
       </c>
       <c r="P97" t="n">
-        <v>0.8764429594502579</v>
+        <v>0.8764429594502577</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -10242,7 +10220,7 @@
         <v>0.58638</v>
       </c>
       <c r="P103" t="n">
-        <v>0.9155674811557055</v>
+        <v>0.9155674811557053</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -10382,7 +10360,7 @@
         <v>0.29838</v>
       </c>
       <c r="P105" t="n">
-        <v>0.8804461556445288</v>
+        <v>0.8804461556445285</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
